--- a/Content/excel.xlsx
+++ b/Content/excel.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\source\repos\Wali0958\EventManagement\Content\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="72" windowWidth="21060" windowHeight="10080"/>
+    <workbookView xWindow="480" yWindow="75" windowWidth="21060" windowHeight="10080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -93,7 +98,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -125,7 +130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -148,29 +153,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -181,6 +174,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -229,7 +225,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -264,7 +260,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -474,22 +470,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.44140625" customWidth="1"/>
-    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -520,11 +516,11 @@
       <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -555,11 +551,11 @@
       <c r="J2" s="4">
         <v>45902</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -590,7 +586,7 @@
       <c r="J3" s="4">
         <v>45902</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -606,7 +602,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -615,7 +611,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
